--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -3638,7 +3638,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="568">
+  <borders count="579">
     <border>
       <left/>
       <right/>
@@ -3649,6 +3649,8 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -4317,6 +4319,8 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -5090,958 +5094,6 @@
     <border/>
     <border/>
     <border/>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
     <border/>
     <border/>
     <border/>
@@ -6391,437 +5443,1396 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
     <border/>
     <border/>
     <border/>
@@ -7529,2228 +7540,2239 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="568">
+  <cellXfs count="579">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0"/>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" xfId="0"/>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="269" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="271" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="273" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="275" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="277" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="279" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="281" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="283" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="285" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="287" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="289" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="291" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="293" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="295" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="297" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="212" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="213" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" xfId="0"/>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="346" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="382" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="217" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="218" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="219" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="220" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="221" xfId="0"/>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="411" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="412" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="413" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="417" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="423" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="426" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="428" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="429" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="431" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="432" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="434" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="435" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="440" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="441" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="442" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="443" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="450" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="452" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="456" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="462" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="464" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="466" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="468" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="470" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="472" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="474" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="476" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="478" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="480" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="484" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="486" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="488" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="490" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="492" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="493" fillId="2" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="494" fillId="3" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="4" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="496" fillId="5" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="497" fillId="6" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="498" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="2" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="3" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="4" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="5" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="6" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="500" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="502" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="504" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" xfId="0"/>
-    <xf numFmtId="0" fontId="506" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="508" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="510" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="512" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="514" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="516" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="518" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="520" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="522" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="524" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="526" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="528" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="530" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="532" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" xfId="0"/>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="600" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="602" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="604" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="606" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="636" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="638" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="642" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="643" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="644" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="645" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="646" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="647" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="648" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="649" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="650" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="651" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="652" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="653" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="654" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="655" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="656" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="657" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="658" fillId="7" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="659" fillId="8" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="660" fillId="9" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="661" fillId="10" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="662" fillId="11" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="663" fillId="12" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="664" fillId="13" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="665" fillId="14" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="466" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="467" xfId="0"/>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="741" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="743" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="745" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="747" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="7" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="8" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="9" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="10" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="11" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="12" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="13" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="14" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="474" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="475" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="476" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="477" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="478" xfId="0"/>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="749" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="750" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="752" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="753" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="755" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="756" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="757" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="758" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="767" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="769" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="771" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="773" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="775" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="777" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="779" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="787" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="791" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="795" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="797" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="799" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="801" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="803" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="805" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="807" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9768,125 +9790,127 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="15.7109375" style="2" customWidth="true"/>
-    <col min="3" max="5" width="14.7109375" style="3" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="3" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="4" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="5" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="41" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="65" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="68" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="71" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="86" t="s">
+      <c r="E5" s="88" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="87" t="s">
+      <c r="D6" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="87" t="s">
+      <c r="E6" s="89" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="97" t="s">
+      <c r="D7" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="98" t="s">
+      <c r="E7" s="100" t="s">
         <v>1</v>
       </c>
     </row>
@@ -9904,154 +9928,156 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="99" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="100" customWidth="true"/>
-    <col min="3" max="5" width="14.7109375" style="101" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="101" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="102" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="103" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="104" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="105" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="142" t="s">
+      <c r="C1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="142" t="s">
+      <c r="D1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="142" t="s">
+      <c r="E1" s="146" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="164" t="s">
+      <c r="C2" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="169" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="166" t="s">
+      <c r="E2" s="170" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="168" t="s">
+      <c r="D3" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="169" t="s">
+      <c r="E3" s="173" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="171" t="s">
+      <c r="D4" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="172" t="s">
+      <c r="E4" s="176" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="189" t="s">
+      <c r="B5" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="190" t="s">
+      <c r="C5" s="194" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="191" t="s">
+      <c r="D5" s="195" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="192" t="s">
+      <c r="E5" s="196" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="198" t="s">
+      <c r="B6" s="202" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="193" t="s">
+      <c r="C6" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="193" t="s">
+      <c r="D6" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="193" t="s">
+      <c r="E6" s="197" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="s">
+      <c r="A7" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="200" t="s">
+      <c r="B7" s="204" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="133" t="s">
+      <c r="C7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="133" t="s">
+      <c r="D7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="133" t="s">
+      <c r="E7" s="137" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="203" t="s">
+      <c r="B8" s="207" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="204" t="s">
+      <c r="C8" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="205" t="s">
+      <c r="D8" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="206" t="s">
+      <c r="E8" s="210" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="215" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10069,159 +10095,162 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="212" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="213" customWidth="true"/>
-    <col min="3" max="6" width="14.7109375" style="214" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="216" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="217" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="218" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="219" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="220" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" style="221" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="266" t="s">
+      <c r="A1" s="273" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="257" t="s">
+      <c r="B1" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="257" t="s">
+      <c r="C1" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="257" t="s">
+      <c r="D1" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="257" t="s">
+      <c r="E1" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="257" t="s">
+      <c r="F1" s="264" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="282" t="s">
+      <c r="B2" s="289" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="283" t="s">
+      <c r="C2" s="290" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="291" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="285" t="s">
+      <c r="E2" s="292" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="286" t="s">
+      <c r="F2" s="293" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="227" t="s">
+      <c r="A3" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="228" t="s">
+      <c r="B3" s="235" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="287" t="s">
+      <c r="C3" s="294" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="295" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="289" t="s">
+      <c r="E3" s="296" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="297" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="233" t="s">
+      <c r="A4" s="240" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="341" t="s">
+      <c r="B4" s="348" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="342" t="s">
+      <c r="C4" s="349" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="343" t="s">
+      <c r="D4" s="350" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="344" t="s">
+      <c r="E4" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="345" t="s">
+      <c r="F4" s="352" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="239" t="s">
+      <c r="A5" s="246" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="312" t="s">
+      <c r="B5" s="319" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="313" t="s">
+      <c r="C5" s="320" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="314" t="s">
+      <c r="D5" s="321" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="315" t="s">
+      <c r="E5" s="322" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="316" t="s">
+      <c r="F5" s="323" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="s">
+      <c r="A6" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="331" t="s">
+      <c r="B6" s="338" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="332" t="s">
+      <c r="C6" s="339" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="333" t="s">
+      <c r="D6" s="340" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="334" t="s">
+      <c r="E6" s="341" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="335" t="s">
+      <c r="F6" s="342" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="251" t="s">
+      <c r="A7" s="258" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="336" t="s">
+      <c r="B7" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="337" t="s">
+      <c r="C7" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="338" t="s">
+      <c r="D7" s="345" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="339" t="s">
+      <c r="E7" s="346" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="340" t="s">
+      <c r="F7" s="347" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="350" t="s">
+      <c r="B8" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="213"/>
-      <c r="F8" s="213"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10238,144 +10267,146 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="351" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="352" customWidth="true"/>
-    <col min="3" max="5" width="14.7109375" style="353" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="358" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="359" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="360" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="361" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="362" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="402" t="s">
+      <c r="A1" s="411" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="394" t="s">
+      <c r="B1" s="403" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="394" t="s">
+      <c r="C1" s="403" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="394" t="s">
+      <c r="D1" s="403" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="394" t="s">
+      <c r="E1" s="403" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="368" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="415" t="s">
+      <c r="B2" s="424" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="416" t="s">
+      <c r="C2" s="425" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="417" t="s">
+      <c r="D2" s="426" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="418" t="s">
+      <c r="E2" s="427" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="364" t="s">
+      <c r="A3" s="373" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="365" t="s">
+      <c r="B3" s="374" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="419" t="s">
+      <c r="C3" s="428" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="420" t="s">
+      <c r="D3" s="429" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="421" t="s">
+      <c r="E3" s="430" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="369" t="s">
+      <c r="A4" s="378" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="457" t="s">
+      <c r="B4" s="466" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="458" t="s">
+      <c r="C4" s="467" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="459" t="s">
+      <c r="D4" s="468" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="460" t="s">
+      <c r="E4" s="469" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="374" t="s">
+      <c r="A5" s="383" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="375" t="s">
+      <c r="B5" s="384" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="425" t="s">
+      <c r="C5" s="434" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="426" t="s">
+      <c r="D5" s="435" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="427" t="s">
+      <c r="E5" s="436" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="379" t="s">
+      <c r="A6" s="388" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="461" t="s">
+      <c r="B6" s="470" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="462" t="s">
+      <c r="C6" s="471" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="463" t="s">
+      <c r="D6" s="472" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="464" t="s">
+      <c r="E6" s="473" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="384" t="s">
+      <c r="A7" s="393" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="450" t="s">
+      <c r="B7" s="459" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="445" t="s">
+      <c r="C7" s="454" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="445" t="s">
+      <c r="D7" s="454" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="445" t="s">
+      <c r="E7" s="454" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="389" t="s">
+      <c r="A8" s="398" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="453" t="s">
+      <c r="B8" s="462" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="454" t="s">
+      <c r="C8" s="463" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="455" t="s">
+      <c r="D8" s="464" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="456" t="s">
+      <c r="E8" s="465" t="s">
         <v>1</v>
       </c>
     </row>
@@ -10393,137 +10424,139 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="465" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="466" customWidth="true"/>
-    <col min="3" max="5" width="14.7109375" style="467" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="474" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="475" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="476" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="477" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="478" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="511" t="s">
+      <c r="A1" s="522" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="503" t="s">
+      <c r="B1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="503" t="s">
+      <c r="C1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="503" t="s">
+      <c r="D1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="503" t="s">
+      <c r="E1" s="514" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="473" t="s">
+      <c r="A2" s="484" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="524" t="s">
+      <c r="B2" s="535" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="525" t="s">
+      <c r="C2" s="536" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="526" t="s">
+      <c r="D2" s="537" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="527" t="s">
+      <c r="E2" s="538" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="478" t="s">
+      <c r="A3" s="489" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="479" t="s">
+      <c r="B3" s="490" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="528" t="s">
+      <c r="C3" s="539" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="529" t="s">
+      <c r="D3" s="540" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="530" t="s">
+      <c r="E3" s="541" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="483" t="s">
+      <c r="A4" s="494" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="484" t="s">
+      <c r="B4" s="495" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="531" t="s">
+      <c r="C4" s="542" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="532" t="s">
+      <c r="D4" s="543" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="533" t="s">
+      <c r="E4" s="544" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="488" t="s">
+      <c r="A5" s="499" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="547" t="s">
+      <c r="B5" s="558" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="548" t="s">
+      <c r="C5" s="559" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="549" t="s">
+      <c r="D5" s="560" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="550" t="s">
+      <c r="E5" s="561" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="493" t="s">
+      <c r="A6" s="504" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="556" t="s">
+      <c r="B6" s="567" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="551" t="s">
+      <c r="C6" s="562" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="551" t="s">
+      <c r="D6" s="562" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="551" t="s">
+      <c r="E6" s="562" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="498" t="s">
+      <c r="A7" s="509" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="559" t="s">
+      <c r="B7" s="570" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="560" t="s">
+      <c r="C7" s="571" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="561" t="s">
+      <c r="D7" s="572" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="562" t="s">
+      <c r="E7" s="573" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="567" t="s">
+      <c r="B8" s="578" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="466"/>
-      <c r="D8" s="466"/>
-      <c r="E8" s="466"/>
+      <c r="C8" s="475"/>
+      <c r="D8" s="475"/>
+      <c r="E8" s="475"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="195" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194" uniqueCount="70">
   <si>
     <t>Table 16. Treatment by Sex</t>
   </si>
@@ -228,15 +228,12 @@
   <si>
     <t>2,149 (35.4%)</t>
   </si>
-  <si>
-    <t>Percentages are row percentages within each treatment group.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="813">
+  <fonts count="666">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2962,607 +2959,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
     </font>
   </fonts>
   <fills count="15">
@@ -3638,7 +3034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="579">
+  <borders count="474">
     <border>
       <left/>
       <right/>
@@ -6831,716 +6227,11 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="579">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -9369,411 +8060,6 @@
     </xf>
     <xf numFmtId="0" fontId="665" fillId="14" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="474" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="475" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="476" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="477" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="478" xfId="0"/>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="741" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="743" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="745" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="747" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="749" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="750" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="752" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="753" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="755" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="756" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="757" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="758" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="767" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="769" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="771" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="773" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="775" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="777" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="779" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="787" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="791" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="795" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="797" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="799" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="801" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="803" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="805" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="807" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -10421,149 +8707,128 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="1.7109375" style="474" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="475" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" style="476" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" style="477" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" style="478" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="522" t="s">
+      <c r="A1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="514" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="514" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="514" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="514" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="484" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="535" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="536" t="s">
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="537" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="538" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="489" t="s">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="490" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="539" t="s">
+      <c r="C3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="540" t="s">
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="541" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="494" t="s">
+      <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="495" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="542" t="s">
+      <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="543" t="s">
+      <c r="D4" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="544" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="499" t="s">
+      <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="558" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="559" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="560" t="s">
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="561" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="504" t="s">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="567" t="s">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="562" t="s">
+      <c r="C6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="562" t="s">
+      <c r="D6" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="562" t="s">
+      <c r="E6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="509" t="s">
+      <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="570" t="s">
+      <c r="B7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="571" t="s">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="572" t="s">
+      <c r="D7" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="573" t="s">
+      <c r="E7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="578" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="475"/>
-      <c r="D8" s="475"/>
-      <c r="E8" s="475"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-  </mergeCells>
 </worksheet>
 </file>
--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="195" uniqueCount="71">
   <si>
     <t>Table 16. Treatment by Sex</t>
   </si>
@@ -228,12 +228,15 @@
   <si>
     <t>2,149 (35.4%)</t>
   </si>
+  <si>
+    <t>Percentages are row percentages within each treatment group.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="666">
+  <fonts count="813">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2959,6 +2962,607 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
     </font>
   </fonts>
   <fills count="15">
@@ -3034,7 +3638,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="474">
+  <borders count="579">
     <border>
       <left/>
       <right/>
@@ -6227,11 +6831,716 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="579">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -8060,6 +9369,411 @@
     </xf>
     <xf numFmtId="0" fontId="665" fillId="14" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="474" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="475" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="476" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="477" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="478" xfId="0"/>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -8707,128 +10421,149 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="474" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="475" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="476" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="477" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="478" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="522" t="s">
         <v>64</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="514" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="484" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="535" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="536" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="537" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="538" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="489" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="490" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="539" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="540" t="s">
         <v>68</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="541" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="494" t="s">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="495" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="542" t="s">
         <v>67</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="543" t="s">
         <v>69</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="544" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="499" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="558" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="559" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="560" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="561" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="504" t="s">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="567" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="562" t="s">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="562" t="s">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="562" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="509" t="s">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="570" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="571" t="s">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="572" t="s">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="573" t="s">
         <v>1</v>
       </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="578" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="475"/>
+      <c r="D8" s="475"/>
+      <c r="E8" s="475"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+  </mergeCells>
 </worksheet>
 </file>
--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -127,7 +127,7 @@
     <t>Event</t>
   </si>
   <si>
-    <t>Pearson's chi-squared test: chi2 = 26.67, p = &lt;0.001</t>
+    <t>Pearson's chi-squared test: chi2 = 26.67, p &lt; 0.001</t>
   </si>
   <si>
     <t>P for trend = &lt;0.001</t>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -11,13 +11,15 @@
     <sheet name="Cross-Tab Styled" sheetId="3" r:id="rId5"/>
     <sheet name="Cross-Tab Trend" sheetId="4" r:id="rId6"/>
     <sheet name="Cross-Tab Row Pct" sheetId="5" r:id="rId7"/>
+    <sheet name="Small Cells Primary" sheetId="6" r:id="rId8"/>
+    <sheet name="Small Cells Complement" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="195" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="257" uniqueCount="87">
   <si>
     <t>Table 16. Treatment by Sex</t>
   </si>
@@ -231,12 +233,60 @@
   <si>
     <t>Percentages are row percentages within each treatment group.</t>
   </si>
+  <si>
+    <t>Small-cell suppression: primary counts only</t>
+  </si>
+  <si>
+    <t>Study group</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>Fisher's exact test: Suppressed</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Counts below 5 are shown as &lt;5; complementary cells are shown as ≥5 to prevent exact reconstruction.</t>
+  </si>
+  <si>
+    <t>Small-cell suppression: complementary protection</t>
+  </si>
+  <si>
+    <t>≥5</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="813">
+  <fonts count="1077">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3413,6 +3463,1088 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
       <name val="Arial"/>
     </font>
     <font>
@@ -3638,7 +4770,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="579">
+  <borders count="769">
     <border>
       <left/>
       <right/>
@@ -7536,11 +8668,1281 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="579">
+  <cellXfs count="769">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -9773,6 +12175,736 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="812" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="579" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="580" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="581" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="582" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="583" xfId="0"/>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="674" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="675" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="676" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="677" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="678" xfId="0"/>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10566,4 +13698,266 @@
     <mergeCell ref="B8:E8"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="579" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="580" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="581" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="582" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="583" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="622" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="614" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="614" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="614" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="614" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="589" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="635" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="636" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="637" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="638" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="594" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="595" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="639" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="640" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="641" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="599" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="600" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="642" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="643" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="644" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="604" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="655" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="656" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="657" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="658" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="609" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="665" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="666" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="667" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="668" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="673" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="674" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="675" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="676" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="677" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="678" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="717" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="709" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="709" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="709" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="709" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="684" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="730" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="731" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="732" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="733" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="689" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="690" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="734" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="735" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="736" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="694" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="695" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="737" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="738" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="739" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="699" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="750" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="751" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="752" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="753" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="704" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="760" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="761" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="762" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="763" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="768" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+  </mergeCells>
+</worksheet>
 </file>